--- a/data/exports/correlation_results.xlsx
+++ b/data/exports/correlation_results.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,16 @@
           <t>Spearman_p</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Significant_Pearson</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Significant_Spearman</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,6 +500,12 @@
       <c r="F2" t="n">
         <v>0</v>
       </c>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -514,6 +530,12 @@
       <c r="F3" t="n">
         <v>0</v>
       </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -538,6 +560,12 @@
       <c r="F4" t="n">
         <v>6.2e-05</v>
       </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -562,6 +590,12 @@
       <c r="F5" t="n">
         <v>0</v>
       </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -586,6 +620,12 @@
       <c r="F6" t="n">
         <v>0</v>
       </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -610,6 +650,12 @@
       <c r="F7" t="n">
         <v>3.1e-05</v>
       </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -634,6 +680,12 @@
       <c r="F8" t="n">
         <v>0</v>
       </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,6 +710,12 @@
       <c r="F9" t="n">
         <v>0</v>
       </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -682,6 +740,12 @@
       <c r="F10" t="n">
         <v>0</v>
       </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -706,6 +770,12 @@
       <c r="F11" t="n">
         <v>0</v>
       </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -730,6 +800,12 @@
       <c r="F12" t="n">
         <v>0</v>
       </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -754,6 +830,12 @@
       <c r="F13" t="n">
         <v>0.580079</v>
       </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -778,6 +860,12 @@
       <c r="F14" t="n">
         <v>0</v>
       </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -802,6 +890,12 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -825,6 +919,12 @@
       </c>
       <c r="F16" t="n">
         <v>6.1e-05</v>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
